--- a/public/file/foglio_verde.xlsx
+++ b/public/file/foglio_verde.xlsx
@@ -1,27 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDREA~1.MBR\AppData\Local\Temp\notes5C8B1E\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STLADMINLOCAL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D25CC2-DC91-4376-8178-81F9EB1FBCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="12" windowWidth="15192" windowHeight="8196"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
     <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -86,9 +98,6 @@
     <t>Rame</t>
   </si>
   <si>
-    <t>(Cu 6,3220)</t>
-  </si>
-  <si>
     <t>posizione</t>
   </si>
   <si>
@@ -185,23 +194,29 @@
     <t xml:space="preserve">PREVENTIVO N° </t>
   </si>
   <si>
-    <t>3CQ-041</t>
-  </si>
-  <si>
-    <t>3CQ-042</t>
+    <t>3CQ-009 I01</t>
+  </si>
+  <si>
+    <t>3CQ-013</t>
+  </si>
+  <si>
+    <t>Valutazione Ecodesign  packeging</t>
+  </si>
+  <si>
+    <t>sostenibili</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,8 +270,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u val="singleAccounting"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial MT"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,8 +290,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="43">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -463,19 +490,198 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -485,14 +691,105 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -500,314 +797,143 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -845,7 +971,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -854,13 +980,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -878,230 +1004,266 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1118,44 +1280,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1176,9 +1329,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1216,9 +1369,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1253,7 +1406,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1288,7 +1441,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1461,8 +1614,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W50"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
@@ -1476,52 +1629,55 @@
     <col min="9" max="9" width="13.77734375" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.88671875" style="11" customWidth="1"/>
-    <col min="12" max="13" width="8.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="11" customWidth="1"/>
-    <col min="16" max="16" width="16" style="11" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.88671875" style="11"/>
+    <col min="12" max="12" width="8.21875" style="11" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="11" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="11" customWidth="1"/>
+    <col min="17" max="17" width="16" style="11" customWidth="1"/>
+    <col min="18" max="18" width="7.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="28.8" customHeight="1" thickBot="1">
-      <c r="A1" s="99" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="100"/>
+    <row r="1" spans="1:23" ht="28.8" customHeight="1" thickBot="1">
+      <c r="A1" s="111" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="112"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="90"/>
+      <c r="E1" s="74"/>
       <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="5"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="101" t="s">
+      <c r="J1" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="102"/>
+      <c r="K1" s="114"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="10"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
       <c r="S1" s="10"/>
       <c r="T1" s="10"/>
       <c r="U1" s="10"/>
-      <c r="V1" s="2"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="V1" s="10"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
@@ -1531,27 +1687,28 @@
         <v>4</v>
       </c>
       <c r="E2" s="14"/>
-      <c r="F2" s="101" t="s">
+      <c r="F2" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="92"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="16"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="121"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="15"/>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
       <c r="U2" s="16"/>
-      <c r="V2" s="14"/>
-    </row>
-    <row r="3" spans="1:22" ht="21" thickBot="1">
+      <c r="V2" s="16"/>
+      <c r="W2" s="14"/>
+    </row>
+    <row r="3" spans="1:23" ht="21" thickBot="1">
       <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
@@ -1565,142 +1722,149 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
       <c r="I3" s="14"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="95"/>
-      <c r="O3" s="95"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="16"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="15"/>
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
       <c r="U3" s="16"/>
-      <c r="V3" s="14"/>
-    </row>
-    <row r="4" spans="1:22" s="81" customFormat="1">
+      <c r="V3" s="16"/>
+      <c r="W3" s="14"/>
+    </row>
+    <row r="4" spans="1:23" s="70" customFormat="1" ht="36.6" customHeight="1">
       <c r="A4" s="76"/>
       <c r="B4" s="77"/>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="116" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="78" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="77" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="106" t="s">
+      <c r="L4" s="79" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="78"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="78" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="79" t="s">
+      <c r="P4" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="78" t="s">
+      <c r="Q4" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="76" t="s">
+      <c r="R4" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="79" t="s">
+      <c r="S4" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="79" t="s">
+      <c r="T4" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="79" t="s">
+      <c r="U4" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="U4" s="79"/>
-      <c r="V4" s="80"/>
-    </row>
-    <row r="5" spans="1:22" s="81" customFormat="1" ht="15" thickBot="1">
-      <c r="A5" s="74" t="s">
+      <c r="V4" s="82"/>
+      <c r="W4" s="81"/>
+    </row>
+    <row r="5" spans="1:23" s="70" customFormat="1" ht="22.2" customHeight="1" thickBot="1">
+      <c r="A5" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="82" t="s">
+      <c r="C5" s="117"/>
+      <c r="D5" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="82" t="str">
+      <c r="F5" s="86">
+        <v>10.6</v>
+      </c>
+      <c r="G5" s="99" t="str">
         <f>CONCATENATE("(Cu ",$B$3,")")</f>
         <v>(Cu )</v>
       </c>
-      <c r="H5" s="82">
+      <c r="H5" s="86">
         <v>1</v>
       </c>
-      <c r="I5" s="82" t="s">
+      <c r="I5" s="86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="82" t="s">
+      <c r="K5" s="119"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="89" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="90" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="107"/>
-      <c r="L5" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="83" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" s="85" t="s">
+      <c r="R5" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="Q5" s="74" t="s">
+      <c r="S5" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="75" t="s">
+      <c r="U5" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="T5" s="75" t="s">
+      <c r="V5" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="U5" s="75" t="s">
+      <c r="W5" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="86" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="24">
         <v>1</v>
       </c>
@@ -1721,1262 +1885,1298 @@
         <f>IF(F6=0,"",H6*B6)</f>
         <v/>
       </c>
-      <c r="J6" s="31"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="10"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="9"/>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="35">
+      <c r="V6" s="10"/>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="34">
         <v>2</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41" t="str">
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40" t="str">
         <f t="shared" ref="G7:G41" si="0">IF(F7=0,"",F7+($B$3-$F$5)*E7)</f>
         <v/>
       </c>
-      <c r="H7" s="40" t="str">
+      <c r="H7" s="39" t="str">
         <f t="shared" ref="H7:H41" si="1">IF($H$5=0,"",IF(F7=0,"",ROUND(G7/$H$5,2)))</f>
         <v/>
       </c>
-      <c r="I7" s="40" t="str">
+      <c r="I7" s="39" t="str">
         <f t="shared" ref="I7:I41" si="2">IF(F7=0,"",H7*B7)</f>
         <v/>
       </c>
-      <c r="J7" s="42"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="16"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="15"/>
       <c r="S7" s="16"/>
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
-      <c r="V7" s="14"/>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="35">
+      <c r="V7" s="16"/>
+      <c r="W7" s="14"/>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="34">
         <v>3</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41" t="str">
+      <c r="B8" s="35"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="40" t="str">
+      <c r="H8" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I8" s="40" t="str">
+      <c r="I8" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="16"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="95"/>
+      <c r="N8" s="95"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="15"/>
       <c r="S8" s="16"/>
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
-      <c r="V8" s="14"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="35">
+      <c r="V8" s="16"/>
+      <c r="W8" s="14"/>
+    </row>
+    <row r="9" spans="1:23" ht="15">
+      <c r="A9" s="34">
         <v>4</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41" t="str">
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="40" t="str">
+      <c r="H9" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I9" s="40" t="str">
+      <c r="I9" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="88"/>
-      <c r="M9" s="88"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="16"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="95"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="15"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
-      <c r="V9" s="14"/>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="35">
+      <c r="V9" s="16"/>
+      <c r="W9" s="14"/>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="34">
         <v>5</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41" t="str">
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="40" t="str">
+      <c r="H10" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I10" s="40" t="str">
+      <c r="I10" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="88"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="16"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="15"/>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="U10" s="16"/>
-      <c r="V10" s="14"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="35">
+      <c r="V10" s="16"/>
+      <c r="W10" s="14"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="34">
         <v>6</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41" t="str">
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="40" t="str">
+      <c r="H11" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I11" s="40" t="str">
+      <c r="I11" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="16"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="95"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="15"/>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
-      <c r="V11" s="14"/>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" s="35">
+      <c r="V11" s="16"/>
+      <c r="W11" s="14"/>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="34">
         <v>7</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41" t="str">
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="40" t="str">
+      <c r="H12" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I12" s="40" t="str">
+      <c r="I12" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="88"/>
-      <c r="M12" s="88"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="88"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="16"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="95"/>
+      <c r="N12" s="95"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="15"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
-      <c r="V12" s="14"/>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13" s="35">
+      <c r="V12" s="16"/>
+      <c r="W12" s="14"/>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="34">
         <v>8</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="str">
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="40" t="str">
+      <c r="H13" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I13" s="40" t="str">
+      <c r="I13" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="88"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="16"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="15"/>
       <c r="S13" s="16"/>
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
-      <c r="V13" s="14"/>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14" s="35">
+      <c r="V13" s="16"/>
+      <c r="W13" s="14"/>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="34">
         <v>9</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41" t="str">
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="40" t="str">
+      <c r="H14" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="40" t="str">
+      <c r="I14" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="88"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="16"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="15"/>
       <c r="S14" s="16"/>
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
-      <c r="V14" s="14"/>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="A15" s="35">
+      <c r="V14" s="16"/>
+      <c r="W14" s="14"/>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="34">
         <v>10</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41" t="str">
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="40" t="str">
+      <c r="H15" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="40" t="str">
+      <c r="I15" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="16"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="15"/>
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
       <c r="U15" s="16"/>
-      <c r="V15" s="14"/>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="35">
+      <c r="V15" s="16"/>
+      <c r="W15" s="14"/>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="34">
         <v>11</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="str">
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H16" s="40" t="str">
+      <c r="H16" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="40" t="str">
+      <c r="I16" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="88"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="16"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="95"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="15"/>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
       <c r="U16" s="16"/>
-      <c r="V16" s="14"/>
-    </row>
-    <row r="17" spans="1:22">
-      <c r="A17" s="35">
+      <c r="V16" s="16"/>
+      <c r="W16" s="14"/>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" s="34">
         <v>12</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41" t="str">
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H17" s="40" t="str">
+      <c r="H17" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="40" t="str">
+      <c r="I17" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="88"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="16"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="15"/>
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
       <c r="U17" s="16"/>
-      <c r="V17" s="14"/>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18" s="35">
+      <c r="V17" s="16"/>
+      <c r="W17" s="14"/>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" s="34">
         <v>13</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41" t="str">
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H18" s="40" t="str">
+      <c r="H18" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="40" t="str">
+      <c r="I18" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="16"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="15"/>
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
       <c r="U18" s="16"/>
-      <c r="V18" s="14"/>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19" s="35">
+      <c r="V18" s="16"/>
+      <c r="W18" s="14"/>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" s="34">
         <v>14</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41" t="str">
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H19" s="40" t="str">
+      <c r="H19" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="40" t="str">
+      <c r="I19" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="16"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="15"/>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
       <c r="U19" s="16"/>
-      <c r="V19" s="14"/>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="35">
+      <c r="V19" s="16"/>
+      <c r="W19" s="14"/>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="34">
         <v>15</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41" t="str">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H20" s="40" t="str">
+      <c r="H20" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="40" t="str">
+      <c r="I20" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J20" s="42"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="88"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="16"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="15"/>
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
       <c r="U20" s="16"/>
-      <c r="V20" s="14"/>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="A21" s="35">
+      <c r="V20" s="16"/>
+      <c r="W20" s="14"/>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" s="34">
         <v>16</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41" t="str">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H21" s="40" t="str">
+      <c r="H21" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="40" t="str">
+      <c r="I21" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J21" s="42"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="16"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="95"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="15"/>
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
       <c r="U21" s="16"/>
-      <c r="V21" s="14"/>
-    </row>
-    <row r="22" spans="1:22">
-      <c r="A22" s="35">
+      <c r="V21" s="16"/>
+      <c r="W21" s="14"/>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" s="34">
         <v>17</v>
       </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41" t="str">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H22" s="40" t="str">
+      <c r="H22" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I22" s="40" t="str">
+      <c r="I22" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J22" s="42"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="88"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="16"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="95"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="15"/>
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
       <c r="U22" s="16"/>
-      <c r="V22" s="14"/>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="A23" s="35">
+      <c r="V22" s="16"/>
+      <c r="W22" s="14"/>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" s="34">
         <v>18</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41" t="str">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H23" s="40" t="str">
+      <c r="H23" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I23" s="40" t="str">
+      <c r="I23" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J23" s="42"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="16"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="15"/>
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
       <c r="U23" s="16"/>
-      <c r="V23" s="14"/>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="35">
+      <c r="V23" s="16"/>
+      <c r="W23" s="14"/>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" s="34">
         <v>19</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41" t="str">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H24" s="40" t="str">
+      <c r="H24" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I24" s="40" t="str">
+      <c r="I24" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J24" s="42"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="88"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="16"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="15"/>
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
       <c r="U24" s="16"/>
-      <c r="V24" s="14"/>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="35">
+      <c r="V24" s="16"/>
+      <c r="W24" s="14"/>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" s="34">
         <v>20</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41" t="str">
+      <c r="B25" s="35"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H25" s="40" t="str">
+      <c r="H25" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I25" s="40" t="str">
+      <c r="I25" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J25" s="42"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="88"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="16"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="15"/>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
       <c r="U25" s="16"/>
-      <c r="V25" s="14"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="35">
+      <c r="V25" s="16"/>
+      <c r="W25" s="14"/>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" s="34">
         <v>21</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="str">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H26" s="40" t="str">
+      <c r="H26" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I26" s="40" t="str">
+      <c r="I26" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J26" s="42"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="16"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="15"/>
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
       <c r="U26" s="16"/>
-      <c r="V26" s="14"/>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="35">
+      <c r="V26" s="16"/>
+      <c r="W26" s="14"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27" s="34">
         <v>22</v>
       </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41" t="str">
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H27" s="40" t="str">
+      <c r="H27" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I27" s="40" t="str">
+      <c r="I27" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="88"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="16"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="15"/>
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
       <c r="U27" s="16"/>
-      <c r="V27" s="14"/>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="35">
+      <c r="V27" s="16"/>
+      <c r="W27" s="14"/>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" s="34">
         <v>23</v>
       </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41" t="str">
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H28" s="40" t="str">
+      <c r="H28" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I28" s="40" t="str">
+      <c r="I28" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J28" s="42"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="88"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="16"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="95"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="15"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
       <c r="U28" s="16"/>
-      <c r="V28" s="14"/>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="A29" s="35">
+      <c r="V28" s="16"/>
+      <c r="W28" s="14"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="34">
         <v>24</v>
       </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41" t="str">
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H29" s="40" t="str">
+      <c r="H29" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I29" s="40" t="str">
+      <c r="I29" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J29" s="42"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="88"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="16"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="95"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="15"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
       <c r="U29" s="16"/>
-      <c r="V29" s="14"/>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="35">
+      <c r="V29" s="16"/>
+      <c r="W29" s="14"/>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="34">
         <v>25</v>
       </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41" t="str">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H30" s="40" t="str">
+      <c r="H30" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I30" s="40" t="str">
+      <c r="I30" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J30" s="42"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="88"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="16"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="95"/>
+      <c r="N30" s="95"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="15"/>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
       <c r="U30" s="16"/>
-      <c r="V30" s="14"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="35">
+      <c r="V30" s="16"/>
+      <c r="W30" s="14"/>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" s="34">
         <v>26</v>
       </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41" t="str">
+      <c r="B31" s="35"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H31" s="40" t="str">
+      <c r="H31" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I31" s="40" t="str">
+      <c r="I31" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J31" s="42"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="88"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="16"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="15"/>
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
       <c r="U31" s="16"/>
-      <c r="V31" s="14"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="35">
+      <c r="V31" s="16"/>
+      <c r="W31" s="14"/>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" s="34">
         <v>27</v>
       </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41" t="str">
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H32" s="40" t="str">
+      <c r="H32" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I32" s="40" t="str">
+      <c r="I32" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J32" s="42"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="16"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="15"/>
       <c r="S32" s="16"/>
       <c r="T32" s="16"/>
       <c r="U32" s="16"/>
-      <c r="V32" s="14"/>
-    </row>
-    <row r="33" spans="1:22">
-      <c r="A33" s="35">
+      <c r="V32" s="16"/>
+      <c r="W32" s="14"/>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" s="34">
         <v>28</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41" t="str">
+      <c r="B33" s="35"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H33" s="40" t="str">
+      <c r="H33" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I33" s="40" t="str">
+      <c r="I33" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J33" s="42"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="44"/>
-      <c r="O33" s="88"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="16"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="15"/>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
       <c r="U33" s="16"/>
-      <c r="V33" s="14"/>
-    </row>
-    <row r="34" spans="1:22">
-      <c r="A34" s="35">
+      <c r="V33" s="16"/>
+      <c r="W33" s="14"/>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" s="34">
         <v>29</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41" t="str">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H34" s="40" t="str">
+      <c r="H34" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I34" s="40" t="str">
+      <c r="I34" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J34" s="42"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="88"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="16"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="15"/>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
       <c r="U34" s="16"/>
-      <c r="V34" s="14"/>
-    </row>
-    <row r="35" spans="1:22">
-      <c r="A35" s="35">
+      <c r="V34" s="16"/>
+      <c r="W34" s="14"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="34">
         <v>30</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="41" t="str">
+      <c r="B35" s="35"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H35" s="40" t="str">
+      <c r="H35" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I35" s="40" t="str">
+      <c r="I35" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J35" s="42"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="88"/>
-      <c r="N35" s="44"/>
-      <c r="O35" s="88"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="16"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="95"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="15"/>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
       <c r="U35" s="16"/>
-      <c r="V35" s="14"/>
-    </row>
-    <row r="36" spans="1:22">
-      <c r="A36" s="35">
+      <c r="V35" s="16"/>
+      <c r="W35" s="14"/>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36" s="34">
         <v>31</v>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="41" t="str">
+      <c r="B36" s="35"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H36" s="40" t="str">
+      <c r="H36" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="40" t="str">
+      <c r="I36" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J36" s="42"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="88"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="16"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="95"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="15"/>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
-      <c r="V36" s="14"/>
-    </row>
-    <row r="37" spans="1:22">
-      <c r="A37" s="35">
+      <c r="V36" s="16"/>
+      <c r="W36" s="14"/>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="34">
         <v>32</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="41" t="str">
+      <c r="B37" s="35"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H37" s="40" t="str">
+      <c r="H37" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I37" s="40" t="str">
+      <c r="I37" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="42"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="88"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="16"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="95"/>
+      <c r="N37" s="95"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="15"/>
       <c r="S37" s="16"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
-      <c r="V37" s="14"/>
-    </row>
-    <row r="38" spans="1:22">
-      <c r="A38" s="35">
+      <c r="V37" s="16"/>
+      <c r="W37" s="14"/>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="34">
         <v>33</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41" t="str">
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H38" s="40" t="str">
+      <c r="H38" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I38" s="40" t="str">
+      <c r="I38" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J38" s="42"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="88"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="88"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="16"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="95"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="15"/>
       <c r="S38" s="16"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
-      <c r="V38" s="14"/>
-    </row>
-    <row r="39" spans="1:22">
-      <c r="A39" s="35">
+      <c r="V38" s="16"/>
+      <c r="W38" s="14"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="34">
         <v>34</v>
       </c>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="41" t="str">
+      <c r="B39" s="35"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H39" s="40" t="str">
+      <c r="H39" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I39" s="40" t="str">
+      <c r="I39" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J39" s="42"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="88"/>
-      <c r="M39" s="88"/>
-      <c r="N39" s="44"/>
-      <c r="O39" s="88"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="16"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="15"/>
       <c r="S39" s="16"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
-      <c r="V39" s="14"/>
-    </row>
-    <row r="40" spans="1:22">
-      <c r="A40" s="35">
+      <c r="V39" s="16"/>
+      <c r="W39" s="14"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="34">
         <v>35</v>
       </c>
-      <c r="B40" s="36"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="41" t="str">
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H40" s="40" t="str">
+      <c r="H40" s="39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I40" s="40" t="str">
+      <c r="I40" s="39" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J40" s="42"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="88"/>
-      <c r="M40" s="88"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="88"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="16"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="95"/>
+      <c r="N40" s="95"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="15"/>
       <c r="S40" s="16"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
-      <c r="V40" s="14"/>
-    </row>
-    <row r="41" spans="1:22" ht="15" thickBot="1">
-      <c r="A41" s="47">
+      <c r="V40" s="16"/>
+      <c r="W40" s="14"/>
+    </row>
+    <row r="41" spans="1:23" ht="15" thickBot="1">
+      <c r="A41" s="45">
         <v>36</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="53" t="str">
+      <c r="B41" s="46"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H41" s="52" t="str">
+      <c r="H41" s="50" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I41" s="52" t="str">
+      <c r="I41" s="50" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J41" s="54"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="89"/>
-      <c r="M41" s="89"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="89"/>
-      <c r="P41" s="57"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="22"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="97"/>
+      <c r="N41" s="97"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="20"/>
       <c r="S41" s="22"/>
       <c r="T41" s="22"/>
       <c r="U41" s="22"/>
-      <c r="V41" s="23"/>
-    </row>
-    <row r="42" spans="1:22">
-      <c r="A42" s="97" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="98"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="23"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="101"/>
       <c r="C42" s="16"/>
       <c r="D42" s="14"/>
       <c r="E42" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H42" s="16"/>
-      <c r="I42" s="101" t="s">
+      <c r="I42" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="115"/>
+      <c r="K42" s="55" t="s">
         <v>33</v>
-      </c>
-      <c r="J42" s="103"/>
-      <c r="K42" s="58" t="s">
-        <v>34</v>
       </c>
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
@@ -2989,24 +3189,25 @@
       <c r="T42" s="16"/>
       <c r="U42" s="16"/>
       <c r="V42" s="16"/>
-    </row>
-    <row r="43" spans="1:22">
-      <c r="A43" s="97" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="98"/>
+      <c r="W42" s="16"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="101"/>
       <c r="C43" s="16"/>
       <c r="D43" s="14"/>
       <c r="E43" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="H43" s="59">
-        <f>SUM(U6:U41)</f>
+        <v>51</v>
+      </c>
+      <c r="H43" s="56">
+        <f>SUM(V6:V41)</f>
         <v>0</v>
       </c>
       <c r="I43" s="15"/>
       <c r="J43" s="16"/>
-      <c r="K43" s="58"/>
+      <c r="K43" s="55"/>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
       <c r="N43" s="16"/>
@@ -3018,26 +3219,27 @@
       <c r="T43" s="16"/>
       <c r="U43" s="16"/>
       <c r="V43" s="16"/>
-    </row>
-    <row r="44" spans="1:22">
-      <c r="A44" s="97" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="98"/>
+      <c r="W43" s="16"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="101"/>
       <c r="C44" s="16"/>
       <c r="D44" s="14"/>
       <c r="E44" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F44" s="16"/>
       <c r="G44" s="16"/>
-      <c r="H44" s="60">
-        <f>SUM(S6:S41)</f>
+      <c r="H44" s="57">
+        <f>SUM(T6:T41)</f>
         <v>0</v>
       </c>
       <c r="I44" s="15"/>
       <c r="J44" s="16"/>
-      <c r="K44" s="61">
+      <c r="K44" s="58">
         <f>SUM(I6:I41)</f>
         <v>0</v>
       </c>
@@ -3052,26 +3254,27 @@
       <c r="T44" s="16"/>
       <c r="U44" s="16"/>
       <c r="V44" s="16"/>
-    </row>
-    <row r="45" spans="1:22" ht="26.4">
+      <c r="W44" s="16"/>
+    </row>
+    <row r="45" spans="1:23" ht="26.4">
       <c r="A45" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="62"/>
+        <v>37</v>
+      </c>
+      <c r="B45" s="59"/>
       <c r="C45" s="16"/>
       <c r="D45" s="14"/>
       <c r="E45" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="16"/>
-      <c r="H45" s="60">
-        <f>SUM(T6:T41)</f>
+      <c r="H45" s="57">
+        <f>SUM(U6:U41)</f>
         <v>0</v>
       </c>
       <c r="I45" s="15"/>
       <c r="J45" s="16"/>
-      <c r="K45" s="58"/>
+      <c r="K45" s="55"/>
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" s="16"/>
@@ -3083,19 +3286,20 @@
       <c r="T45" s="16"/>
       <c r="U45" s="16"/>
       <c r="V45" s="16"/>
-    </row>
-    <row r="46" spans="1:22" ht="15" thickBot="1">
-      <c r="A46" s="97"/>
-      <c r="B46" s="98"/>
+      <c r="W45" s="16"/>
+    </row>
+    <row r="46" spans="1:23" ht="15" thickBot="1">
+      <c r="A46" s="100"/>
+      <c r="B46" s="101"/>
       <c r="C46" s="16"/>
       <c r="D46" s="14"/>
       <c r="E46" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F46" s="22"/>
       <c r="G46" s="16"/>
-      <c r="H46" s="60">
-        <f>SUM(V6:V41)</f>
+      <c r="H46" s="57">
+        <f>SUM(W6:W41)</f>
         <v>0</v>
       </c>
       <c r="I46" s="20"/>
@@ -3112,153 +3316,120 @@
       <c r="T46" s="16"/>
       <c r="U46" s="16"/>
       <c r="V46" s="16"/>
-    </row>
-    <row r="47" spans="1:22" ht="14.4" customHeight="1">
-      <c r="A47" s="108" t="s">
+      <c r="W46" s="16"/>
+    </row>
+    <row r="47" spans="1:23" ht="14.4" customHeight="1">
+      <c r="A47" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="103"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="109"/>
-      <c r="C47" s="109"/>
-      <c r="D47" s="109"/>
-      <c r="E47" s="110"/>
-      <c r="F47" s="24" t="s">
+      <c r="G47" s="24"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="G47" s="24"/>
-      <c r="H47" s="63"/>
-      <c r="I47" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="65"/>
-      <c r="K47" s="66"/>
-      <c r="L47" s="66"/>
-      <c r="M47" s="66"/>
-      <c r="N47" s="66"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="16"/>
+      <c r="J47" s="62"/>
       <c r="Q47" s="16"/>
       <c r="R47" s="16"/>
       <c r="S47" s="16"/>
       <c r="T47" s="16"/>
       <c r="U47" s="16"/>
       <c r="V47" s="16"/>
-    </row>
-    <row r="48" spans="1:22">
-      <c r="A48" s="111"/>
-      <c r="B48" s="112"/>
-      <c r="C48" s="112"/>
-      <c r="D48" s="112"/>
-      <c r="E48" s="113"/>
-      <c r="F48" s="35" t="s">
+      <c r="W47" s="16"/>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="105"/>
+      <c r="B48" s="106"/>
+      <c r="C48" s="106"/>
+      <c r="D48" s="106"/>
+      <c r="E48" s="107"/>
+      <c r="F48" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="34"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="G48" s="35"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="J48" s="69"/>
-      <c r="K48" s="66"/>
-      <c r="L48" s="66"/>
-      <c r="M48" s="66"/>
-      <c r="N48" s="66"/>
-      <c r="O48" s="66"/>
-      <c r="P48" s="16"/>
+      <c r="J48" s="65"/>
       <c r="Q48" s="16"/>
       <c r="R48" s="16"/>
       <c r="S48" s="16"/>
       <c r="T48" s="16"/>
       <c r="U48" s="16"/>
       <c r="V48" s="16"/>
-    </row>
-    <row r="49" spans="1:22" ht="26.4">
-      <c r="A49" s="111"/>
-      <c r="B49" s="112"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="113"/>
-      <c r="F49" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="G49" s="35"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="66"/>
-      <c r="L49" s="66"/>
-      <c r="M49" s="66"/>
-      <c r="N49" s="66"/>
-      <c r="O49" s="66"/>
-      <c r="P49" s="16"/>
+      <c r="W48" s="16"/>
+    </row>
+    <row r="49" spans="1:23" ht="26.4">
+      <c r="A49" s="105"/>
+      <c r="B49" s="106"/>
+      <c r="C49" s="106"/>
+      <c r="D49" s="106"/>
+      <c r="E49" s="107"/>
+      <c r="F49" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" s="34"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="64"/>
+      <c r="J49" s="65"/>
       <c r="Q49" s="16"/>
       <c r="R49" s="16"/>
       <c r="S49" s="16"/>
       <c r="T49" s="16"/>
       <c r="U49" s="16"/>
       <c r="V49" s="16"/>
-    </row>
-    <row r="50" spans="1:22" ht="15" thickBot="1">
-      <c r="A50" s="114"/>
-      <c r="B50" s="115"/>
-      <c r="C50" s="115"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="116"/>
+      <c r="W49" s="16"/>
+    </row>
+    <row r="50" spans="1:23" ht="15" thickBot="1">
+      <c r="A50" s="108"/>
+      <c r="B50" s="109"/>
+      <c r="C50" s="109"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="110"/>
       <c r="F50" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G50" s="20"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="72"/>
-      <c r="K50" s="66"/>
-      <c r="L50" s="66"/>
-      <c r="M50" s="66"/>
-      <c r="N50" s="66"/>
-      <c r="O50" s="66"/>
-      <c r="P50" s="16"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="68"/>
       <c r="Q50" s="16"/>
       <c r="R50" s="16"/>
       <c r="S50" s="16"/>
       <c r="T50" s="16"/>
       <c r="U50" s="16"/>
-      <c r="V50" s="73"/>
-    </row>
-    <row r="51" spans="1:22">
-      <c r="K51" s="66"/>
-      <c r="L51" s="66"/>
-      <c r="M51" s="66"/>
-      <c r="N51" s="66"/>
-      <c r="O51" s="66"/>
-      <c r="P51" s="66"/>
-      <c r="Q51" s="66"/>
-      <c r="R51" s="66"/>
-      <c r="S51" s="66"/>
-      <c r="T51" s="66"/>
-      <c r="U51" s="66"/>
-      <c r="V51" s="66"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:B1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="J2:Q3"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:E50"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
@@ -3267,7 +3438,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
